--- a/raw/processedSamples/20260519_r3_CMH_USDA-blood_Nano-QuIC.xlsx
+++ b/raw/processedSamples/20260519_r3_CMH_USDA-blood_Nano-QuIC.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FEBF9F-BEC3-4D04-B743-1B0606E330AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0DF19D-84E9-4358-9D99-5E6E5320202F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="1" r:id="rId1"/>
     <sheet name="Table All Cycles" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -545,7 +545,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -560,6 +560,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -767,7 +775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -823,6 +831,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2832,297 +2843,297 @@
       </c>
     </row>
     <row r="13" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="22" t="s">
         <v>167</v>
       </c>
       <c r="B13" s="16"/>
-      <c r="C13" s="17">
+      <c r="C13" s="5">
         <v>1000</v>
       </c>
-      <c r="D13" s="17">
-        <v>100</v>
-      </c>
-      <c r="E13" s="17">
-        <v>100</v>
-      </c>
-      <c r="F13" s="17">
-        <v>100</v>
-      </c>
-      <c r="G13" s="17">
-        <v>100</v>
-      </c>
-      <c r="H13" s="17">
-        <v>100</v>
-      </c>
-      <c r="I13" s="17">
-        <v>100</v>
-      </c>
-      <c r="J13" s="17">
-        <v>100</v>
-      </c>
-      <c r="K13" s="17">
-        <v>100</v>
-      </c>
-      <c r="L13" s="17">
-        <v>100</v>
-      </c>
-      <c r="M13" s="17">
-        <v>100</v>
-      </c>
-      <c r="N13" s="17">
-        <v>100</v>
-      </c>
-      <c r="O13" s="17">
+      <c r="D13" s="6">
+        <v>4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>4</v>
+      </c>
+      <c r="F13" s="6">
+        <v>4</v>
+      </c>
+      <c r="G13" s="6">
+        <v>4</v>
+      </c>
+      <c r="H13" s="6">
+        <v>4</v>
+      </c>
+      <c r="I13" s="6">
+        <v>4</v>
+      </c>
+      <c r="J13" s="6">
+        <v>4</v>
+      </c>
+      <c r="K13" s="6">
+        <v>4</v>
+      </c>
+      <c r="L13" s="6">
+        <v>4</v>
+      </c>
+      <c r="M13" s="6">
+        <v>4</v>
+      </c>
+      <c r="N13" s="6">
+        <v>4</v>
+      </c>
+      <c r="O13" s="5">
         <v>1000</v>
       </c>
-      <c r="P13" s="17">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="17">
-        <v>100</v>
-      </c>
-      <c r="R13" s="17">
-        <v>100</v>
-      </c>
-      <c r="S13" s="17">
-        <v>100</v>
-      </c>
-      <c r="T13" s="17">
-        <v>100</v>
-      </c>
-      <c r="U13" s="17">
-        <v>100</v>
-      </c>
-      <c r="V13" s="17">
-        <v>100</v>
-      </c>
-      <c r="W13" s="17">
-        <v>100</v>
-      </c>
-      <c r="X13" s="17">
-        <v>100</v>
-      </c>
-      <c r="Y13" s="17">
-        <v>100</v>
-      </c>
-      <c r="Z13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AA13" s="17">
+      <c r="P13" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>4</v>
+      </c>
+      <c r="R13" s="6">
+        <v>4</v>
+      </c>
+      <c r="S13" s="6">
+        <v>4</v>
+      </c>
+      <c r="T13" s="6">
+        <v>4</v>
+      </c>
+      <c r="U13" s="6">
+        <v>4</v>
+      </c>
+      <c r="V13" s="6">
+        <v>4</v>
+      </c>
+      <c r="W13" s="6">
+        <v>4</v>
+      </c>
+      <c r="X13" s="6">
+        <v>4</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>4</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AA13" s="5">
         <v>1000</v>
       </c>
-      <c r="AB13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AC13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AD13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AE13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AF13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AG13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AH13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AI13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AJ13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AK13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AL13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AM13" s="17">
+      <c r="AB13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AC13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM13" s="5">
         <v>1000</v>
       </c>
-      <c r="AN13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AO13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AP13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AQ13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AR13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AS13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AT13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AU13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AV13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AW13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AX13" s="17">
-        <v>100</v>
-      </c>
-      <c r="AY13" s="17">
+      <c r="AN13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AP13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AQ13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AR13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AS13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AT13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AU13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AV13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AW13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AX13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AY13" s="5">
         <v>1000</v>
       </c>
-      <c r="AZ13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BA13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BB13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BC13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BD13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BE13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BF13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BG13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BH13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BI13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BJ13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BK13" s="17">
+      <c r="AZ13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BA13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BB13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BC13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BD13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BE13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BF13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BG13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BH13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BI13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BJ13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BK13" s="5">
         <v>1000</v>
       </c>
-      <c r="BL13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BM13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BN13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BO13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BP13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BQ13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BR13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BS13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BT13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BU13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BV13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BW13" s="17">
+      <c r="BL13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BM13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BN13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BO13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BP13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BQ13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BR13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BS13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BT13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BU13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BV13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BW13" s="5">
         <v>1000</v>
       </c>
-      <c r="BX13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BY13" s="17">
-        <v>100</v>
-      </c>
-      <c r="BZ13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CA13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CB13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CC13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CD13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CE13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CF13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CG13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CH13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CI13" s="17">
+      <c r="BX13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BY13" s="6">
+        <v>4</v>
+      </c>
+      <c r="BZ13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CA13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CB13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CC13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CD13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CE13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CF13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CG13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CH13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CI13" s="5">
         <v>1000</v>
       </c>
-      <c r="CJ13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CK13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CL13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CM13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CN13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CO13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CP13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CQ13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CR13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CS13" s="17">
-        <v>100</v>
-      </c>
-      <c r="CT13" s="9">
-        <v>100</v>
+      <c r="CJ13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CK13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CL13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CM13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CN13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CO13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CP13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CQ13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CR13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CS13" s="6">
+        <v>4</v>
+      </c>
+      <c r="CT13" s="6">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:98" ht="30" x14ac:dyDescent="0.25">
